--- a/top_resume_matches_full_details.xlsx
+++ b/top_resume_matches_full_details.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
   <si>
     <t>name</t>
   </si>
@@ -58,118 +58,88 @@
     <t>Govinda Gupta</t>
   </si>
   <si>
-    <t>Tanisha Kumari</t>
-  </si>
-  <si>
     <t>Kunal Kumar</t>
   </si>
   <si>
-    <t>Omkar Shirpure</t>
+    <t>Vinay Shrivastava</t>
   </si>
   <si>
     <t>ag6420564@gmail.com</t>
   </si>
   <si>
-    <t>tanishak2266@gmail.com</t>
-  </si>
-  <si>
     <t>kunalroy199915@gmail.com</t>
   </si>
   <si>
-    <t>22b0910@iitb.ac.in</t>
+    <t>vinayshrivastava613@gmail.com</t>
   </si>
   <si>
     <t>+919399600645</t>
   </si>
   <si>
-    <t>+91 9608954838</t>
-  </si>
-  <si>
     <t>+91-8709198459</t>
   </si>
   <si>
-    <t>null</t>
+    <t>+91-7470431954</t>
   </si>
   <si>
     <t>Medi-Caps University</t>
   </si>
   <si>
-    <t>Indian Institute of Technology (IIT) Bombay</t>
-  </si>
-  <si>
     <t>Arya College of Engineering &amp; IT, Jaipur</t>
   </si>
   <si>
-    <t>Indian Institute of Technology Bombay</t>
+    <t>Sagar Group of Institutions - SISTec</t>
   </si>
   <si>
     <t>Excellent Communication Problem Solving Object Oriented Programming Data Structures and Algorithm C/C++ Java Python HTML CSS JavaScript MySQL Machine Learning</t>
   </si>
   <si>
-    <t>Data Science Numpy Matplotlib MATLAB PyTorch Pandas NLTK SQL PostgreSQL PowerBI TensorFlow OpenCV</t>
-  </si>
-  <si>
     <t>Python Web Development Machine Learning Django flask FAST Api Rest Api Deep Learning MySQL ORM Kafka Spark Redis TensorFlow Pytorch YOLO NumPy Pandas Skit learn Lang chain Beautiful Sofy Git GitHub Gitlab AWS LLM MariaDB JavaScript Node.js React PostgreSQL</t>
   </si>
   <si>
-    <t>C/C++ Python Go Scala Haskell Lisp Bash x86 and MIPS Assembly VHDL DART Verilog React Next.js Flutter Node.js Django MongoDB PostgreSQL Angular Excel NumPy Pandas MatPlotLib SciPy PyTorch TensorFlow scikit-learn Kubernetes Docker Redis ELK Stack HiveDB MATLAB Git Sed Awk GDB</t>
+    <t>HTML CSS JAVASCRIPT REACT.JS PYTHON(Basic) MACHINE LEARNING</t>
   </si>
   <si>
     <t>2024</t>
   </si>
   <si>
+    <t>2022</t>
+  </si>
+  <si>
     <t>2025</t>
   </si>
   <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>2026</t>
-  </si>
-  <si>
     <t>['JavaScript for Beginners', 'Blue Prism Foundation Trainning', 'Blue Prism Associate Developer', 'Crash Course on Python', 'Data Structures', 'C/C++ for Competitive Programming']</t>
   </si>
   <si>
-    <t>['Machine Learning: Unsupervised Learning Recommenders and Reinforcement Learning', 'Supervised Machine Learning: Regression and Classifications', 'Advanced learning algorithm', 'Excel: Excel Skills for Business: Essentials', 'Excel: Excel Skills for Business: Intermediate I', 'Excel: Excel Skills for Business: Intermediate II', 'Excel: Excel Skills for Business: Advanced']</t>
-  </si>
-  <si>
     <t>[]</t>
   </si>
   <si>
-    <t>extracted_resumes\resumes_20250410_205744\Resumes_15\Govinda Gupta Resume .pdf</t>
-  </si>
-  <si>
-    <t>extracted_resumes\resumes_20250410_205744\Resumes_15\Tanisha_ Kumari.pdf</t>
-  </si>
-  <si>
-    <t>extracted_resumes\resumes_20250410_205744\Resumes_15\Kunal_CV_Python__.pdf</t>
-  </si>
-  <si>
-    <t>extracted_resumes\resumes_20250410_205744\Resumes_15\resume.pdf</t>
+    <t>extracted_resumes\resumes_20250414_190924\Resumes_15\Govinda Gupta Resume .pdf</t>
+  </si>
+  <si>
+    <t>extracted_resumes\resumes_20250414_190924\Resumes_15\Kunal_CV_Python__.pdf</t>
+  </si>
+  <si>
+    <t>extracted_resumes\resumes_20250414_190924\Resumes_15\Main Resume.pdf</t>
   </si>
   <si>
     <t>Govinda Gupta Resume .pdf</t>
   </si>
   <si>
-    <t>Tanisha_ Kumari.pdf</t>
-  </si>
-  <si>
     <t>Kunal_CV_Python__.pdf</t>
   </si>
   <si>
-    <t>resume.pdf</t>
+    <t>Main Resume.pdf</t>
   </si>
   <si>
     <t>Excellent Communication Problem Solving Object Oriented Programming Data Structures and Algorithm C/C++ Java Python HTML CSS JavaScript MySQL Machine Learning 0 0 2024 Medi-Caps University</t>
   </si>
   <si>
-    <t>Data Science Numpy Matplotlib MATLAB PyTorch Pandas NLTK SQL PostgreSQL PowerBI TensorFlow OpenCV 0 0 2025 Indian Institute of Technology (IIT) Bombay</t>
-  </si>
-  <si>
     <t>Python Web Development Machine Learning Django flask FAST Api Rest Api Deep Learning MySQL ORM Kafka Spark Redis TensorFlow Pytorch YOLO NumPy Pandas Skit learn Lang chain Beautiful Sofy Git GitHub Gitlab AWS LLM MariaDB JavaScript Node.js React PostgreSQL 1 0 2022 Arya College of Engineering &amp; IT, Jaipur</t>
   </si>
   <si>
-    <t>C/C++ Python Go Scala Haskell Lisp Bash x86 and MIPS Assembly VHDL DART Verilog React Next.js Flutter Node.js Django MongoDB PostgreSQL Angular Excel NumPy Pandas MatPlotLib SciPy PyTorch TensorFlow scikit-learn Kubernetes Docker Redis ELK Stack HiveDB MATLAB Git Sed Awk GDB 0 0 2026 Indian Institute of Technology Bombay</t>
+    <t>HTML CSS JAVASCRIPT REACT.JS PYTHON(Basic) MACHINE LEARNING 0 0 2025 Sagar Group of Institutions - SISTec</t>
   </si>
 </sst>
 </file>
@@ -527,7 +497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -576,22 +546,22 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
         <v>25</v>
       </c>
-      <c r="E2" t="s">
-        <v>29</v>
-      </c>
       <c r="F2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -600,16 +570,16 @@
         <v>0</v>
       </c>
       <c r="J2" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="K2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="L2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="M2">
-        <v>0.3940578037533906</v>
+        <v>0.4706003396873037</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -617,40 +587,40 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
         <v>26</v>
       </c>
-      <c r="E3" t="s">
-        <v>30</v>
-      </c>
       <c r="F3" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="K3" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L3" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="M3">
-        <v>0.3822581735968827</v>
+        <v>0.4036580228329465</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -658,81 +628,40 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
         <v>27</v>
       </c>
-      <c r="E4" t="s">
-        <v>31</v>
-      </c>
       <c r="F4" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G4" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="K4" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="L4" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="M4">
-        <v>0.361308548817636</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5" t="s">
-        <v>43</v>
-      </c>
-      <c r="K5" t="s">
-        <v>47</v>
-      </c>
-      <c r="L5" t="s">
-        <v>51</v>
-      </c>
-      <c r="M5">
-        <v>0.3263307312726218</v>
+        <v>0.3033374519469124</v>
       </c>
     </row>
   </sheetData>

--- a/top_resume_matches_full_details.xlsx
+++ b/top_resume_matches_full_details.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>name</t>
   </si>
@@ -61,54 +61,36 @@
     <t>Kunal Kumar</t>
   </si>
   <si>
-    <t>Vinay Shrivastava</t>
-  </si>
-  <si>
     <t>ag6420564@gmail.com</t>
   </si>
   <si>
     <t>kunalroy199915@gmail.com</t>
   </si>
   <si>
-    <t>vinayshrivastava613@gmail.com</t>
-  </si>
-  <si>
     <t>+919399600645</t>
   </si>
   <si>
     <t>+91-8709198459</t>
   </si>
   <si>
-    <t>+91-7470431954</t>
-  </si>
-  <si>
     <t>Medi-Caps University</t>
   </si>
   <si>
     <t>Arya College of Engineering &amp; IT, Jaipur</t>
   </si>
   <si>
-    <t>Sagar Group of Institutions - SISTec</t>
-  </si>
-  <si>
     <t>Excellent Communication Problem Solving Object Oriented Programming Data Structures and Algorithm C/C++ Java Python HTML CSS JavaScript MySQL Machine Learning</t>
   </si>
   <si>
     <t>Python Web Development Machine Learning Django flask FAST Api Rest Api Deep Learning MySQL ORM Kafka Spark Redis TensorFlow Pytorch YOLO NumPy Pandas Skit learn Lang chain Beautiful Sofy Git GitHub Gitlab AWS LLM MariaDB JavaScript Node.js React PostgreSQL</t>
   </si>
   <si>
-    <t>HTML CSS JAVASCRIPT REACT.JS PYTHON(Basic) MACHINE LEARNING</t>
-  </si>
-  <si>
     <t>2024</t>
   </si>
   <si>
     <t>2022</t>
   </si>
   <si>
-    <t>2025</t>
-  </si>
-  <si>
     <t>['JavaScript for Beginners', 'Blue Prism Foundation Trainning', 'Blue Prism Associate Developer', 'Crash Course on Python', 'Data Structures', 'C/C++ for Competitive Programming']</t>
   </si>
   <si>
@@ -121,25 +103,16 @@
     <t>extracted_resumes\resumes_20250414_190924\Resumes_15\Kunal_CV_Python__.pdf</t>
   </si>
   <si>
-    <t>extracted_resumes\resumes_20250414_190924\Resumes_15\Main Resume.pdf</t>
-  </si>
-  <si>
     <t>Govinda Gupta Resume .pdf</t>
   </si>
   <si>
     <t>Kunal_CV_Python__.pdf</t>
   </si>
   <si>
-    <t>Main Resume.pdf</t>
-  </si>
-  <si>
     <t>Excellent Communication Problem Solving Object Oriented Programming Data Structures and Algorithm C/C++ Java Python HTML CSS JavaScript MySQL Machine Learning 0 0 2024 Medi-Caps University</t>
   </si>
   <si>
     <t>Python Web Development Machine Learning Django flask FAST Api Rest Api Deep Learning MySQL ORM Kafka Spark Redis TensorFlow Pytorch YOLO NumPy Pandas Skit learn Lang chain Beautiful Sofy Git GitHub Gitlab AWS LLM MariaDB JavaScript Node.js React PostgreSQL 1 0 2022 Arya College of Engineering &amp; IT, Jaipur</t>
-  </si>
-  <si>
-    <t>HTML CSS JAVASCRIPT REACT.JS PYTHON(Basic) MACHINE LEARNING 0 0 2025 Sagar Group of Institutions - SISTec</t>
   </si>
 </sst>
 </file>
@@ -497,7 +470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -546,22 +519,22 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
         <v>19</v>
       </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
       <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" t="s">
         <v>25</v>
-      </c>
-      <c r="F2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" t="s">
-        <v>31</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -570,16 +543,16 @@
         <v>0</v>
       </c>
       <c r="J2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="K2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="M2">
-        <v>0.4706003396873037</v>
+        <v>0.386223145664524</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -587,22 +560,22 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
         <v>20</v>
       </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
       <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s">
         <v>26</v>
-      </c>
-      <c r="F3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" t="s">
-        <v>32</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -611,57 +584,16 @@
         <v>0</v>
       </c>
       <c r="J3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="K3" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="L3" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="M3">
-        <v>0.4036580228329465</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4" t="s">
-        <v>35</v>
-      </c>
-      <c r="K4" t="s">
-        <v>38</v>
-      </c>
-      <c r="L4" t="s">
-        <v>41</v>
-      </c>
-      <c r="M4">
-        <v>0.3033374519469124</v>
+        <v>0.3293343309615394</v>
       </c>
     </row>
   </sheetData>

--- a/top_resume_matches_full_details.xlsx
+++ b/top_resume_matches_full_details.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>name</t>
   </si>
@@ -58,58 +58,88 @@
     <t>Govinda Gupta</t>
   </si>
   <si>
+    <t>Tanisha Kumari</t>
+  </si>
+  <si>
     <t>Kunal Kumar</t>
   </si>
   <si>
     <t>ag6420564@gmail.com</t>
   </si>
   <si>
+    <t>tanishak2266@gmail.com</t>
+  </si>
+  <si>
     <t>kunalroy199915@gmail.com</t>
   </si>
   <si>
     <t>+919399600645</t>
   </si>
   <si>
+    <t>+91 9608954838</t>
+  </si>
+  <si>
     <t>+91-8709198459</t>
   </si>
   <si>
     <t>Medi-Caps University</t>
   </si>
   <si>
+    <t>Indian Institute of Technology (IIT) Bombay</t>
+  </si>
+  <si>
     <t>Arya College of Engineering &amp; IT, Jaipur</t>
   </si>
   <si>
     <t>Excellent Communication Problem Solving Object Oriented Programming Data Structures and Algorithm C/C++ Java Python HTML CSS JavaScript MySQL Machine Learning</t>
   </si>
   <si>
+    <t>Data Science Numpy Matplotlib MATLAB PyTorch Pandas NLTK SQL PostgreSQL PowerBI TensorFlow OpenCV</t>
+  </si>
+  <si>
     <t>Python Web Development Machine Learning Django flask FAST Api Rest Api Deep Learning MySQL ORM Kafka Spark Redis TensorFlow Pytorch YOLO NumPy Pandas Skit learn Lang chain Beautiful Sofy Git GitHub Gitlab AWS LLM MariaDB JavaScript Node.js React PostgreSQL</t>
   </si>
   <si>
     <t>2024</t>
   </si>
   <si>
+    <t>2025</t>
+  </si>
+  <si>
     <t>2022</t>
   </si>
   <si>
     <t>['JavaScript for Beginners', 'Blue Prism Foundation Trainning', 'Blue Prism Associate Developer', 'Crash Course on Python', 'Data Structures', 'C/C++ for Competitive Programming']</t>
   </si>
   <si>
+    <t>['Machine Learning: Unsupervised Learning Recommenders and Reinforcement Learning', 'Supervised Machine Learning: Regression and Classifications', 'Advanced learning algorithm', 'Excel: Excel Skills for Business: Essentials', 'Excel: Excel Skills for Business: Intermediate I', 'Excel: Excel Skills for Business: Intermediate II', 'Excel: Excel Skills for Business: Advanced']</t>
+  </si>
+  <si>
     <t>[]</t>
   </si>
   <si>
     <t>extracted_resumes\resumes_20250414_190924\Resumes_15\Govinda Gupta Resume .pdf</t>
   </si>
   <si>
+    <t>extracted_resumes\resumes_20250414_190924\Resumes_15\Tanisha_ Kumari.pdf</t>
+  </si>
+  <si>
     <t>extracted_resumes\resumes_20250414_190924\Resumes_15\Kunal_CV_Python__.pdf</t>
   </si>
   <si>
     <t>Govinda Gupta Resume .pdf</t>
   </si>
   <si>
+    <t>Tanisha_ Kumari.pdf</t>
+  </si>
+  <si>
     <t>Kunal_CV_Python__.pdf</t>
   </si>
   <si>
     <t>Excellent Communication Problem Solving Object Oriented Programming Data Structures and Algorithm C/C++ Java Python HTML CSS JavaScript MySQL Machine Learning 0 0 2024 Medi-Caps University</t>
+  </si>
+  <si>
+    <t>Data Science Numpy Matplotlib MATLAB PyTorch Pandas NLTK SQL PostgreSQL PowerBI TensorFlow OpenCV 0 0 2025 Indian Institute of Technology (IIT) Bombay</t>
   </si>
   <si>
     <t>Python Web Development Machine Learning Django flask FAST Api Rest Api Deep Learning MySQL ORM Kafka Spark Redis TensorFlow Pytorch YOLO NumPy Pandas Skit learn Lang chain Beautiful Sofy Git GitHub Gitlab AWS LLM MariaDB JavaScript Node.js React PostgreSQL 1 0 2022 Arya College of Engineering &amp; IT, Jaipur</t>
@@ -470,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -519,22 +549,22 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -543,16 +573,16 @@
         <v>0</v>
       </c>
       <c r="J2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="K2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="L2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="M2">
-        <v>0.386223145664524</v>
+        <v>0.3914125874513502</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -560,40 +590,81 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="K3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M3">
+        <v>0.3604311874042069</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" t="s">
         <v>30</v>
       </c>
-      <c r="L3" t="s">
-        <v>32</v>
-      </c>
-      <c r="M3">
-        <v>0.3293343309615394</v>
+      <c r="G4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M4">
+        <v>0.3478121299735076</v>
       </c>
     </row>
   </sheetData>

--- a/top_resume_matches_full_details.xlsx
+++ b/top_resume_matches_full_details.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
   <si>
     <t>name</t>
   </si>
@@ -58,91 +58,88 @@
     <t>Govinda Gupta</t>
   </si>
   <si>
-    <t>Tanisha Kumari</t>
-  </si>
-  <si>
     <t>Kunal Kumar</t>
   </si>
   <si>
+    <t>Omkar Shirpure</t>
+  </si>
+  <si>
     <t>ag6420564@gmail.com</t>
   </si>
   <si>
-    <t>tanishak2266@gmail.com</t>
-  </si>
-  <si>
     <t>kunalroy199915@gmail.com</t>
   </si>
   <si>
+    <t>22b0910@iitb.ac.in</t>
+  </si>
+  <si>
     <t>+919399600645</t>
   </si>
   <si>
-    <t>+91 9608954838</t>
-  </si>
-  <si>
     <t>+91-8709198459</t>
   </si>
   <si>
+    <t>null</t>
+  </si>
+  <si>
     <t>Medi-Caps University</t>
   </si>
   <si>
-    <t>Indian Institute of Technology (IIT) Bombay</t>
-  </si>
-  <si>
     <t>Arya College of Engineering &amp; IT, Jaipur</t>
   </si>
   <si>
+    <t>Indian Institute of Technology Bombay</t>
+  </si>
+  <si>
     <t>Excellent Communication Problem Solving Object Oriented Programming Data Structures and Algorithm C/C++ Java Python HTML CSS JavaScript MySQL Machine Learning</t>
   </si>
   <si>
-    <t>Data Science Numpy Matplotlib MATLAB PyTorch Pandas NLTK SQL PostgreSQL PowerBI TensorFlow OpenCV</t>
-  </si>
-  <si>
     <t>Python Web Development Machine Learning Django flask FAST Api Rest Api Deep Learning MySQL ORM Kafka Spark Redis TensorFlow Pytorch YOLO NumPy Pandas Skit learn Lang chain Beautiful Sofy Git GitHub Gitlab AWS LLM MariaDB JavaScript Node.js React PostgreSQL</t>
   </si>
   <si>
+    <t>C/C++ Python Go Scala Haskell Lisp Bash x86 and MIPS Assembly VHDL DART Verilog React Next.js Flutter Node.js Django MongoDB PostgreSQL Angular Excel NumPy Pandas MatPlotLib SciPy PyTorch TensorFlow scikit-learn Kubernetes Docker Redis ELK Stack HiveDB MATLAB Git Sed Awk GDB</t>
+  </si>
+  <si>
     <t>2024</t>
   </si>
   <si>
-    <t>2025</t>
-  </si>
-  <si>
     <t>2022</t>
   </si>
   <si>
+    <t>2026</t>
+  </si>
+  <si>
     <t>['JavaScript for Beginners', 'Blue Prism Foundation Trainning', 'Blue Prism Associate Developer', 'Crash Course on Python', 'Data Structures', 'C/C++ for Competitive Programming']</t>
   </si>
   <si>
-    <t>['Machine Learning: Unsupervised Learning Recommenders and Reinforcement Learning', 'Supervised Machine Learning: Regression and Classifications', 'Advanced learning algorithm', 'Excel: Excel Skills for Business: Essentials', 'Excel: Excel Skills for Business: Intermediate I', 'Excel: Excel Skills for Business: Intermediate II', 'Excel: Excel Skills for Business: Advanced']</t>
-  </si>
-  <si>
     <t>[]</t>
   </si>
   <si>
     <t>extracted_resumes\resumes_20250414_190924\Resumes_15\Govinda Gupta Resume .pdf</t>
   </si>
   <si>
-    <t>extracted_resumes\resumes_20250414_190924\Resumes_15\Tanisha_ Kumari.pdf</t>
-  </si>
-  <si>
     <t>extracted_resumes\resumes_20250414_190924\Resumes_15\Kunal_CV_Python__.pdf</t>
   </si>
   <si>
+    <t>extracted_resumes\resumes_20250414_190924\Resumes_15\resume.pdf</t>
+  </si>
+  <si>
     <t>Govinda Gupta Resume .pdf</t>
   </si>
   <si>
-    <t>Tanisha_ Kumari.pdf</t>
-  </si>
-  <si>
     <t>Kunal_CV_Python__.pdf</t>
   </si>
   <si>
+    <t>resume.pdf</t>
+  </si>
+  <si>
     <t>Excellent Communication Problem Solving Object Oriented Programming Data Structures and Algorithm C/C++ Java Python HTML CSS JavaScript MySQL Machine Learning 0 0 2024 Medi-Caps University</t>
   </si>
   <si>
-    <t>Data Science Numpy Matplotlib MATLAB PyTorch Pandas NLTK SQL PostgreSQL PowerBI TensorFlow OpenCV 0 0 2025 Indian Institute of Technology (IIT) Bombay</t>
-  </si>
-  <si>
     <t>Python Web Development Machine Learning Django flask FAST Api Rest Api Deep Learning MySQL ORM Kafka Spark Redis TensorFlow Pytorch YOLO NumPy Pandas Skit learn Lang chain Beautiful Sofy Git GitHub Gitlab AWS LLM MariaDB JavaScript Node.js React PostgreSQL 1 0 2022 Arya College of Engineering &amp; IT, Jaipur</t>
+  </si>
+  <si>
+    <t>C/C++ Python Go Scala Haskell Lisp Bash x86 and MIPS Assembly VHDL DART Verilog React Next.js Flutter Node.js Django MongoDB PostgreSQL Angular Excel NumPy Pandas MatPlotLib SciPy PyTorch TensorFlow scikit-learn Kubernetes Docker Redis ELK Stack HiveDB MATLAB Git Sed Awk GDB 0 0 2026 Indian Institute of Technology Bombay</t>
   </si>
 </sst>
 </file>
@@ -573,16 +570,16 @@
         <v>0</v>
       </c>
       <c r="J2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M2">
-        <v>0.3914125874513502</v>
+        <v>0.4563015789653803</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -608,22 +605,22 @@
         <v>32</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M3">
-        <v>0.3604311874042069</v>
+        <v>0.4336836569276473</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -646,25 +643,25 @@
         <v>30</v>
       </c>
       <c r="G4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M4">
-        <v>0.3478121299735076</v>
+        <v>0.3347215714206931</v>
       </c>
     </row>
   </sheetData>

--- a/top_resume_matches_full_details.xlsx
+++ b/top_resume_matches_full_details.xlsx
@@ -579,7 +579,7 @@
         <v>39</v>
       </c>
       <c r="M2">
-        <v>0.4563015789653803</v>
+        <v>0.4157756012412562</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -620,7 +620,7 @@
         <v>40</v>
       </c>
       <c r="M3">
-        <v>0.4336836569276473</v>
+        <v>0.4067337876127337</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -661,7 +661,7 @@
         <v>41</v>
       </c>
       <c r="M4">
-        <v>0.3347215714206931</v>
+        <v>0.3551404235646088</v>
       </c>
     </row>
   </sheetData>

--- a/top_resume_matches_full_details.xlsx
+++ b/top_resume_matches_full_details.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>name</t>
   </si>
@@ -55,91 +55,64 @@
     <t>similarity_score</t>
   </si>
   <si>
+    <t>Manisha Hirasing Rathod</t>
+  </si>
+  <si>
     <t>Govinda Gupta</t>
   </si>
   <si>
-    <t>Kunal Kumar</t>
-  </si>
-  <si>
-    <t>Omkar Shirpure</t>
+    <t>maniishaarathod@gmail.com</t>
   </si>
   <si>
     <t>ag6420564@gmail.com</t>
   </si>
   <si>
-    <t>kunalroy199915@gmail.com</t>
-  </si>
-  <si>
-    <t>22b0910@iitb.ac.in</t>
+    <t>9307744151</t>
   </si>
   <si>
     <t>+919399600645</t>
   </si>
   <si>
-    <t>+91-8709198459</t>
-  </si>
-  <si>
-    <t>null</t>
+    <t>MKSSS’s Cummins College of Engineering for Women, Pune</t>
   </si>
   <si>
     <t>Medi-Caps University</t>
   </si>
   <si>
-    <t>Arya College of Engineering &amp; IT, Jaipur</t>
-  </si>
-  <si>
-    <t>Indian Institute of Technology Bombay</t>
+    <t>DATA STRUCTURE AND ALGORITHM OBJECT ORIENTED PROGRAMMING JAVA C and C++ DATABASE MANAGEMENT SYSTEM MYSQL MACHINE LEARNING DEEP LEARNING HTML</t>
   </si>
   <si>
     <t>Excellent Communication Problem Solving Object Oriented Programming Data Structures and Algorithm C/C++ Java Python HTML CSS JavaScript MySQL Machine Learning</t>
   </si>
   <si>
-    <t>Python Web Development Machine Learning Django flask FAST Api Rest Api Deep Learning MySQL ORM Kafka Spark Redis TensorFlow Pytorch YOLO NumPy Pandas Skit learn Lang chain Beautiful Sofy Git GitHub Gitlab AWS LLM MariaDB JavaScript Node.js React PostgreSQL</t>
-  </si>
-  <si>
-    <t>C/C++ Python Go Scala Haskell Lisp Bash x86 and MIPS Assembly VHDL DART Verilog React Next.js Flutter Node.js Django MongoDB PostgreSQL Angular Excel NumPy Pandas MatPlotLib SciPy PyTorch TensorFlow scikit-learn Kubernetes Docker Redis ELK Stack HiveDB MATLAB Git Sed Awk GDB</t>
+    <t>2025</t>
   </si>
   <si>
     <t>2024</t>
   </si>
   <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>2026</t>
+    <t>['Cummins Soft Skill Certificate']</t>
   </si>
   <si>
     <t>['JavaScript for Beginners', 'Blue Prism Foundation Trainning', 'Blue Prism Associate Developer', 'Crash Course on Python', 'Data Structures', 'C/C++ for Competitive Programming']</t>
   </si>
   <si>
-    <t>[]</t>
+    <t>extracted_resumes\resumes_20250423_112919\Resume\SDE _Normal Format.docx</t>
   </si>
   <si>
     <t>extracted_resumes\resumes_20250414_190924\Resumes_15\Govinda Gupta Resume .pdf</t>
   </si>
   <si>
-    <t>extracted_resumes\resumes_20250414_190924\Resumes_15\Kunal_CV_Python__.pdf</t>
-  </si>
-  <si>
-    <t>extracted_resumes\resumes_20250414_190924\Resumes_15\resume.pdf</t>
+    <t>SDE _Normal Format.docx</t>
   </si>
   <si>
     <t>Govinda Gupta Resume .pdf</t>
   </si>
   <si>
-    <t>Kunal_CV_Python__.pdf</t>
-  </si>
-  <si>
-    <t>resume.pdf</t>
+    <t>DATA STRUCTURE AND ALGORITHM OBJECT ORIENTED PROGRAMMING JAVA C and C++ DATABASE MANAGEMENT SYSTEM MYSQL MACHINE LEARNING DEEP LEARNING HTML 0 0 2025 MKSSS’s Cummins College of Engineering for Women, Pune</t>
   </si>
   <si>
     <t>Excellent Communication Problem Solving Object Oriented Programming Data Structures and Algorithm C/C++ Java Python HTML CSS JavaScript MySQL Machine Learning 0 0 2024 Medi-Caps University</t>
-  </si>
-  <si>
-    <t>Python Web Development Machine Learning Django flask FAST Api Rest Api Deep Learning MySQL ORM Kafka Spark Redis TensorFlow Pytorch YOLO NumPy Pandas Skit learn Lang chain Beautiful Sofy Git GitHub Gitlab AWS LLM MariaDB JavaScript Node.js React PostgreSQL 1 0 2022 Arya College of Engineering &amp; IT, Jaipur</t>
-  </si>
-  <si>
-    <t>C/C++ Python Go Scala Haskell Lisp Bash x86 and MIPS Assembly VHDL DART Verilog React Next.js Flutter Node.js Django MongoDB PostgreSQL Angular Excel NumPy Pandas MatPlotLib SciPy PyTorch TensorFlow scikit-learn Kubernetes Docker Redis ELK Stack HiveDB MATLAB Git Sed Awk GDB 0 0 2026 Indian Institute of Technology Bombay</t>
   </si>
 </sst>
 </file>
@@ -497,7 +470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -546,22 +519,22 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
         <v>19</v>
       </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
       <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" t="s">
         <v>25</v>
-      </c>
-      <c r="F2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" t="s">
-        <v>31</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -570,16 +543,16 @@
         <v>0</v>
       </c>
       <c r="J2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="K2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="M2">
-        <v>0.4157756012412562</v>
+        <v>0.4745373644319609</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -587,81 +560,40 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
         <v>20</v>
       </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
       <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s">
         <v>26</v>
       </c>
-      <c r="F3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" t="s">
-        <v>32</v>
-      </c>
       <c r="H3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="K3" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="L3" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="M3">
-        <v>0.4067337876127337</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4" t="s">
-        <v>35</v>
-      </c>
-      <c r="K4" t="s">
-        <v>38</v>
-      </c>
-      <c r="L4" t="s">
-        <v>41</v>
-      </c>
-      <c r="M4">
-        <v>0.3551404235646088</v>
+        <v>0.434277723258</v>
       </c>
     </row>
   </sheetData>
